--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484134_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484134_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. BALTÀ CASTELLTORT</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3426</v>
+        <v>5.2184</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2403</v>
+        <v>3.399</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1023</v>
+        <v>1.8194</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7594</v>
+        <v>3.4121</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3358</v>
+        <v>-0.8063</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4237</v>
+        <v>4.2184</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0564</v>
+        <v>3.6944</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4554</v>
+        <v>-0.3619</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3991</v>
+        <v>4.0563</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.297</v>
+        <v>-0.2823</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1197</v>
+        <v>-0.4444</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8227</v>
+        <v>0.162</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7855</v>
+        <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3216</v>
+        <v>0.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3661</v>
+        <v>0.3629</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9555</v>
+        <v>-0.0129</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.532</v>
+        <v>0.266</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8097</v>
+        <v>0.532</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3417</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3271</v>
+        <v>3.6945</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9285</v>
+        <v>1.1241</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3986</v>
+        <v>2.5704</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4121</v>
+        <v>5.1381</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8063</v>
+        <v>-1.3305</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2184</v>
+        <v>6.4686</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6944</v>
+        <v>4.1451</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3619</v>
+        <v>-0.6845</v>
       </c>
       <c r="L3" t="n">
-        <v>4.0563</v>
+        <v>4.8296</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2823</v>
+        <v>0.993</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4444</v>
+        <v>-0.646</v>
       </c>
       <c r="O3" t="n">
-        <v>0.162</v>
+        <v>1.639</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1903</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1903</v>
+        <v>-2.9758</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5413</v>
+        <v>0.0127</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1076</v>
+        <v>-0.0452</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4337</v>
+        <v>0.058</v>
       </c>
       <c r="V3" t="n">
-        <v>0.266</v>
+        <v>-0.266</v>
       </c>
       <c r="W3" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>-0.266</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>A. BALTÀ CASTELLTORT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7879</v>
+        <v>3.3898</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2456</v>
+        <v>3.7925</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5424</v>
+        <v>-0.4027</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1381</v>
+        <v>1.7594</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3305</v>
+        <v>1.3358</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4686</v>
+        <v>0.4237</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1451</v>
+        <v>2.0564</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6845</v>
+        <v>2.4554</v>
       </c>
       <c r="L4" t="n">
-        <v>4.8296</v>
+        <v>-0.3991</v>
       </c>
       <c r="M4" t="n">
-        <v>0.993</v>
+        <v>-0.297</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.646</v>
+        <v>-1.1197</v>
       </c>
       <c r="O4" t="n">
-        <v>1.639</v>
+        <v>0.8227</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8939</v>
+        <v>1.3688</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9238</v>
+        <v>0.9183</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0299</v>
+        <v>0.4505</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.266</v>
+        <v>-0.532</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-2.3417</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>C. FONS TEIXIDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5826</v>
+        <v>3.2651</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6699</v>
+        <v>4.1753</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0873</v>
+        <v>-0.9102</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5185</v>
+        <v>3.968</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8398</v>
+        <v>0.3173</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3213</v>
+        <v>3.6508</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3135</v>
+        <v>5.7566</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1102</v>
+        <v>1.4516</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2034</v>
+        <v>4.3049</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.795</v>
+        <v>-1.7885</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2704</v>
+        <v>-1.1343</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.6542</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.1822</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>1.056</v>
+        <v>0.7695</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9353</v>
+        <v>0.6009</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1207</v>
+        <v>0.1686</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6032</v>
+        <v>-1.4724</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. FONS TEIXIDO</t>
+          <t>J. MARBÀ RECASENS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5483</v>
+        <v>2.4835</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7671</v>
+        <v>1.245</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2188</v>
+        <v>1.2385</v>
       </c>
       <c r="G6" t="n">
-        <v>3.968</v>
+        <v>1.6531</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3173</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6508</v>
+        <v>1.6531</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7566</v>
+        <v>1.245</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4516</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4.3049</v>
+        <v>1.245</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7885</v>
+        <v>0.4081</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1343</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6542</v>
+        <v>0.4081</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1822</v>
+        <v>0.1984</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0527</v>
+        <v>-0.0425</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1928</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.14</v>
+        <v>-0.0425</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4724</v>
+        <v>0.6745</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4724</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARBÀ RECASENS</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4274</v>
+        <v>2.2025</v>
       </c>
       <c r="E7" t="n">
-        <v>1.245</v>
+        <v>2.2618</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1824</v>
+        <v>-0.0592</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6531</v>
+        <v>1.5185</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.8398</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6531</v>
+        <v>-0.3213</v>
       </c>
       <c r="J7" t="n">
-        <v>1.245</v>
+        <v>3.3135</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.1102</v>
       </c>
       <c r="L7" t="n">
-        <v>1.245</v>
+        <v>0.2034</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4081</v>
+        <v>-1.795</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.2704</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4081</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1984</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.676</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.5272</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.1488</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6745</v>
+        <v>0.6032</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>O. VILADRICH SENSERRICH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0238</v>
+        <v>0.6041</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0951</v>
+        <v>0.0402</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1189</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7856</v>
+        <v>0.4483</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2068</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4211</v>
+        <v>0.4483</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7738</v>
+        <v>0.0402</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4952</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2786</v>
+        <v>0.0402</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0119</v>
+        <v>0.4081</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7116</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6997</v>
+        <v>0.4081</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1661</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.579</v>
+        <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8646</v>
+        <v>-0.0425</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1063</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7582</v>
+        <v>-0.0425</v>
       </c>
       <c r="V8" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. VILADRICH SENSERRICH</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.548</v>
+        <v>0.3712</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0402</v>
+        <v>0.1365</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5079</v>
+        <v>0.2348</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4483</v>
+        <v>1.4524</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-2.0416</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4483</v>
+        <v>3.4941</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0402</v>
+        <v>1.6789</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0402</v>
+        <v>2.5353</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4081</v>
+        <v>-0.2265</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.1853</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4081</v>
+        <v>0.9588</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1984</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.5059</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.2268</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.279</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0151</v>
+        <v>-1.3119</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.334</v>
+        <v>-0.1156</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3189</v>
+        <v>-1.1963</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4524</v>
+        <v>-1.6387</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0416</v>
+        <v>-0.1462</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4941</v>
+        <v>-1.4925</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6789</v>
+        <v>-0.4387</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8564000000000001</v>
+        <v>0.121</v>
       </c>
       <c r="L10" t="n">
-        <v>2.5353</v>
+        <v>-0.5597</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2265</v>
+        <v>-1.2</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1853</v>
+        <v>-0.2672</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9588</v>
+        <v>-0.9328</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9758</v>
+        <v>-0.1984</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1196</v>
+        <v>0.7397</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2436</v>
+        <v>0.5215</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3632</v>
+        <v>0.2182</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2065</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.766</v>
+        <v>-1.4492</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6258</v>
+        <v>-3.1753</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1402</v>
+        <v>1.7261</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6387</v>
+        <v>-1.7856</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1462</v>
+        <v>-2.2068</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4925</v>
+        <v>0.4211</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4387</v>
+        <v>-1.7738</v>
       </c>
       <c r="K11" t="n">
-        <v>0.121</v>
+        <v>-1.4952</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5597</v>
+        <v>-0.2786</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2</v>
+        <v>-0.0119</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2672</v>
+        <v>-0.7116</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9328</v>
+        <v>0.6997</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7935</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1984</v>
+        <v>-4.1661</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9919</v>
+        <v>2.579</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2857</v>
+        <v>1.3915</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0113</v>
+        <v>1.0261</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2743</v>
+        <v>0.3654</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2065</v>
+        <v>0.532</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.7384</v>
       </c>
       <c r="X11" t="n">
         <v>-1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1676</v>
+        <v>-1.5171</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2498</v>
+        <v>-1.7397</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0822</v>
+        <v>0.2225</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5493</v>
@@ -1390,13 +1390,13 @@
         <v>0.7935</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4279</v>
+        <v>0.2225</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3117</v>
+        <v>0.1984</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1162</v>
+        <v>0.0241</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.639</v>
+        <v>16.9509</v>
       </c>
       <c r="E13" t="n">
-        <v>10.8319</v>
+        <v>11.1438</v>
       </c>
       <c r="F13" t="n">
-        <v>5.807300000000001</v>
+        <v>5.8073</v>
       </c>
       <c r="G13" t="n">
         <v>15.3763</v>
@@ -1453,7 +1453,7 @@
         <v>-4.3871</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.918099999999999</v>
+        <v>-7.9181</v>
       </c>
       <c r="O13" t="n">
         <v>3.5309</v>
@@ -1468,10 +1468,10 @@
         <v>15.8708</v>
       </c>
       <c r="S13" t="n">
-        <v>5.6399</v>
+        <v>5.9516</v>
       </c>
       <c r="T13" t="n">
-        <v>4.025100000000001</v>
+        <v>4.336900000000001</v>
       </c>
       <c r="U13" t="n">
         <v>1.6147</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8575</v>
+        <v>7.0353</v>
       </c>
       <c r="E14" t="n">
-        <v>9.9572</v>
+        <v>8.834899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0997</v>
+        <v>-1.7995</v>
       </c>
       <c r="G14" t="n">
         <v>2.8266</v>
@@ -1546,13 +1546,13 @@
         <v>3.5709</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5232</v>
+        <v>-0.299</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2358</v>
+        <v>0.1135</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7126</v>
+        <v>-0.4125</v>
       </c>
       <c r="V14" t="n">
         <v>1.1352</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2619</v>
+        <v>0.4439</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6166</v>
+        <v>0.7187</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3547</v>
+        <v>-0.2748</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2731</v>
@@ -1624,13 +1624,13 @@
         <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6553</v>
+        <v>-0.4733</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5611</v>
+        <v>-0.4591</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0142</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8925</v>
+        <v>-1.281</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4806</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.373</v>
+        <v>-1.3534</v>
       </c>
       <c r="G16" t="n">
         <v>-3.1464</v>
@@ -1702,13 +1702,13 @@
         <v>2.7774</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2024</v>
+        <v>-0.5909</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2495</v>
+        <v>-0.1586</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4519</v>
+        <v>-0.4323</v>
       </c>
       <c r="V16" t="n">
         <v>0.8692</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9206</v>
+        <v>-1.9933</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4719</v>
+        <v>-0.9161</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5513</v>
+        <v>-1.0772</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.4543</v>
+        <v>-2.3371</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1114</v>
+        <v>-1.7036</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.3429</v>
+        <v>-0.6335</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.0934</v>
+        <v>-0.6895</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2674</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.3608</v>
+        <v>-0.1154</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3609</v>
+        <v>-1.6476</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3788</v>
+        <v>-1.1295</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.9821</v>
+        <v>-0.5182</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1741</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1372</v>
+        <v>-1.1081</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1248</v>
+        <v>-0.2266</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.262</v>
+        <v>-0.8815</v>
       </c>
       <c r="V17" t="n">
-        <v>2.6789</v>
+        <v>-0.532</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6789</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8078</v>
+        <v>-2.0669</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4263</v>
+        <v>-2.778</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3816</v>
+        <v>0.7111</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3371</v>
+        <v>-5.4543</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7036</v>
+        <v>-0.1114</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6335</v>
+        <v>-5.3429</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6895</v>
+        <v>-3.0934</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5741000000000001</v>
+        <v>0.2674</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1154</v>
+        <v>-3.3608</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6476</v>
+        <v>-2.3609</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1295</v>
+        <v>-0.3788</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5182</v>
+        <v>-1.9821</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>3.1741</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9226</v>
+        <v>-0.2834</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7368</v>
+        <v>-0.1813</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1858</v>
+        <v>-0.1021</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.532</v>
+        <v>2.6789</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.301</v>
+        <v>-4.1428</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3486</v>
+        <v>-2.2466</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9523</v>
+        <v>-1.8962</v>
       </c>
       <c r="G19" t="n">
         <v>-4.2084</v>
@@ -1936,13 +1936,13 @@
         <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4217</v>
+        <v>-0.2636</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1303</v>
+        <v>-0.0283</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2914</v>
+        <v>-0.2353</v>
       </c>
       <c r="V19" t="n">
         <v>-0.266</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.7396</v>
+        <v>-5.3493</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2784</v>
+        <v>-1.9723</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4612</v>
+        <v>-3.377</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4742</v>
@@ -2014,13 +2014,13 @@
         <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0832</v>
+        <v>-0.6929</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4988</v>
+        <v>-0.1927</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5844</v>
+        <v>-0.5003</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6032</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.097200000000001</v>
+        <v>-7.9247</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.336499999999999</v>
+        <v>-7.5203</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7607</v>
+        <v>-0.4044</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3094</v>
@@ -2092,13 +2092,13 @@
         <v>2.9758</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7407</v>
+        <v>-0.5682</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2979</v>
+        <v>-0.4817</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4428</v>
+        <v>-0.0866</v>
       </c>
       <c r="V21" t="n">
         <v>-1.881</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-16.6393</v>
+        <v>-15.2788</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.807299999999998</v>
+        <v>-5.8073</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.8319</v>
+        <v>-9.471399999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-15.3763</v>
       </c>
       <c r="H22" t="n">
-        <v>4.0568</v>
+        <v>4.056799999999999</v>
       </c>
       <c r="I22" t="n">
         <v>-19.433</v>
@@ -2161,7 +2161,7 @@
         <v>-15.9021</v>
       </c>
       <c r="P22" t="n">
-        <v>2.975699999999999</v>
+        <v>2.9757</v>
       </c>
       <c r="Q22" t="n">
         <v>-15.8707</v>
@@ -2170,13 +2170,13 @@
         <v>18.8465</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.639900000000001</v>
+        <v>-4.2794</v>
       </c>
       <c r="T22" t="n">
         <v>-1.6148</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.0251</v>
+        <v>-2.6648</v>
       </c>
       <c r="V22" t="n">
         <v>1.4011</v>
